--- a/data/dividends_info_20260712.xlsx
+++ b/data/dividends_info_20260712.xlsx
@@ -4190,7 +4190,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CASTELLO SGR S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4241,7 +4241,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4275,7 +4275,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4292,7 +4292,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>CASTELLO SGR S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4445,7 +4445,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4455,14 +4455,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4472,14 +4472,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4489,14 +4489,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4506,14 +4506,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4530,7 +4530,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4540,14 +4540,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4557,14 +4557,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4581,7 +4581,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4598,7 +4598,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4608,14 +4608,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4625,14 +4625,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4642,14 +4642,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4659,14 +4659,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4676,14 +4676,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4710,14 +4710,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4727,14 +4727,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4744,14 +4744,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4761,14 +4761,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4778,14 +4778,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4802,7 +4802,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4812,14 +4812,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4836,7 +4836,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4853,7 +4853,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4870,7 +4870,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4880,14 +4880,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4897,14 +4897,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4921,7 +4921,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4938,7 +4938,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4948,14 +4948,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4972,7 +4972,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4989,7 +4989,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5006,7 +5006,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5016,14 +5016,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5033,14 +5033,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5057,7 +5057,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5067,14 +5067,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5084,14 +5084,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5101,14 +5101,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5125,7 +5125,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5135,14 +5135,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5159,7 +5159,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5169,14 +5169,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5193,7 +5193,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5210,7 +5210,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5220,14 +5220,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5244,7 +5244,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5261,7 +5261,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5278,7 +5278,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5288,14 +5288,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5312,7 +5312,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5329,7 +5329,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5346,7 +5346,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5363,7 +5363,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5397,7 +5397,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5414,7 +5414,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5424,14 +5424,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5441,14 +5441,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5526,14 +5526,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5550,7 +5550,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5560,14 +5560,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5577,14 +5577,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5594,14 +5594,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5611,14 +5611,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5628,14 +5628,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5652,7 +5652,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5662,14 +5662,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5679,14 +5679,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5703,7 +5703,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5720,7 +5720,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5737,7 +5737,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5771,7 +5771,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5805,7 +5805,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5815,14 +5815,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5839,7 +5839,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5856,7 +5856,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5890,7 +5890,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5907,7 +5907,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5917,14 +5917,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5958,7 +5958,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5975,7 +5975,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5985,14 +5985,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6019,14 +6019,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6060,7 +6060,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6070,14 +6070,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6087,14 +6087,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6111,7 +6111,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6128,7 +6128,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -6155,14 +6155,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6179,7 +6179,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6213,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6230,7 +6230,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6240,14 +6240,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6257,14 +6257,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6281,7 +6281,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6298,7 +6298,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6308,14 +6308,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6332,7 +6332,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6383,7 +6383,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6393,14 +6393,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6444,14 +6444,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6461,14 +6461,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6478,14 +6478,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6502,7 +6502,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6512,14 +6512,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6536,7 +6536,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6546,14 +6546,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6587,7 +6587,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6621,7 +6621,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6631,14 +6631,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6648,14 +6648,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6672,7 +6672,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6682,14 +6682,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6706,7 +6706,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6716,14 +6716,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6733,14 +6733,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
